--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260730.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.27%</t>
+          <t>10.75%</t>
         </is>
       </c>
     </row>
@@ -638,51 +638,51 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.98%</t>
+          <t>10.24%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>VRT US</t>
+          <t>PWR US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>維諦技術控股公司</t>
+          <t>廣達服務公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>90,325</t>
+          <t>35,555</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>7.91%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>PWR US</t>
+          <t>VRT US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>廣達服務公司</t>
+          <t>維諦技術控股公司</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>35,555</t>
+          <t>90,325</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.03%</t>
+          <t>6.94%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>6.08%</t>
+          <t>5.80%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.72%</t>
+          <t>4.43%</t>
         </is>
       </c>
     </row>
@@ -748,95 +748,95 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.81%</t>
+          <t>3.59%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>19,379</t>
+          <t>48,995</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.15%</t>
+          <t>3.43%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>D US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>道明尼能源公司</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>117,083</t>
+          <t>19,379</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>48,995</t>
+          <t>58,959</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.83%</t>
+          <t>2.88%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>D US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>道明尼能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>58,959</t>
+          <t>117,083</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.47%</t>
+          <t>2.34%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.26%</t>
+          <t>2.10%</t>
         </is>
       </c>
     </row>
@@ -902,51 +902,51 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.01%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>XEL US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Xcel 能源</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>62,303</t>
+          <t>24,304</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.73%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>XEL US</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Xcel 能源</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>24,304</t>
+          <t>62,303</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.65%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.36%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
@@ -1056,139 +1056,139 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.25%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>MTZ US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>MasTec公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>32,510</t>
+          <t>11,337</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>47,027</t>
+          <t>32,510</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>30,445</t>
+          <t>47,027</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MTZ US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>MasTec公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>11,337</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.15%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>95,063</t>
+          <t>30,445</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.11%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>95,063</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.12%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.07%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1232,90 +1232,90 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>0.99%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>75,074</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.96%</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>PPL公司</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>145,945</t>
+          <t>75,074</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>EVRG US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Evergy公司</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>30,314</t>
+          <t>145,945</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.88%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>EVRG US</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>Evergy公司</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>30,314</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -1327,88 +1327,88 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>ENS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>EnerSys</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>13,252</t>
+          <t>9,004</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>ENS US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>EnerSys</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>9,004</t>
+          <t>13,252</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>202609ESU6</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>小型S＆P 500股價指數</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>202609ESU6</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>小型S＆P 500股價指數</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1430,51 +1430,51 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>43,483</t>
+          <t>25,781</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>25,781</t>
+          <t>43,483</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.65%</t>
+          <t>0.62%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.61%</t>
         </is>
       </c>
     </row>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.55%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>94,502</t>
+          <t>6,827</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.48%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>6,827</t>
+          <t>94,502</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.38%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.27%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>115,374,017</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
